--- a/executa_obma/Resultados Planilha/comparacao_irace_vs_padrao_MDGb.xlsx
+++ b/executa_obma/Resultados Planilha/comparacao_irace_vs_padrao_MDGb.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\irace\resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\irace\resultados\Resultados Planilha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB08870-84BF-4398-A47B-659BFCE296FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C402F62-C5CC-433B-9536-2DDB9BAD31A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Instância</t>
   </si>
@@ -65,13 +65,16 @@
   </si>
   <si>
     <t>MDG-b_40</t>
+  </si>
+  <si>
+    <t>Great Cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +90,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -96,7 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,15 +130,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -442,7 +468,7 @@
     <col min="5" max="5" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,8 +484,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -475,8 +504,11 @@
       <c r="E2">
         <v>13.361433</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>11286776</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -492,8 +524,11 @@
       <c r="E3">
         <v>15.050224</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>11290874</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -509,8 +544,11 @@
       <c r="E4">
         <v>14.932698</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>11292296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -526,8 +564,11 @@
       <c r="E5">
         <v>12.779260000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>11279916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -543,8 +584,11 @@
       <c r="E6">
         <v>14.131883</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>11296415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -560,8 +604,11 @@
       <c r="E7">
         <v>13.967318000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>11279820</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -577,8 +624,11 @@
       <c r="E8">
         <v>15.3178</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>11281245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -594,8 +644,11 @@
       <c r="E9">
         <v>14.402089</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>11289469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -611,8 +664,11 @@
       <c r="E10">
         <v>13.073345</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>11288571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -628,6 +684,12 @@
       <c r="E11">
         <v>13.498547</v>
       </c>
+      <c r="F11">
+        <v>11307105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
